--- a/giro_da_praça_ofertas - SEXTA A DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SEXTA A DOMINGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A74A03-59C4-4D58-92F6-29A292E4203E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F968576A-5223-48BE-9911-9AAB42A37BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -428,7 +425,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,6 +436,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -469,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -493,6 +496,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1670,11 +1682,11 @@
       <c r="C51" s="3">
         <v>161871</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="E51" s="10"/>
+      <c r="F51" s="11">
         <v>7.49</v>
       </c>
     </row>
@@ -1688,11 +1700,11 @@
       <c r="C52" s="3">
         <v>104406</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7">
+      <c r="E52" s="10"/>
+      <c r="F52" s="11">
         <v>10.49</v>
       </c>
     </row>
@@ -1706,11 +1718,11 @@
       <c r="C53" s="3">
         <v>104424</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
+      <c r="E53" s="10"/>
+      <c r="F53" s="11">
         <v>8.99</v>
       </c>
     </row>
@@ -1724,11 +1736,11 @@
       <c r="C54" s="3">
         <v>122984</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="7">
+      <c r="E54" s="10"/>
+      <c r="F54" s="11">
         <v>9.49</v>
       </c>
     </row>
@@ -1742,11 +1754,11 @@
       <c r="C55" s="3">
         <v>102282</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="7">
+      <c r="E55" s="10"/>
+      <c r="F55" s="11">
         <v>8.69</v>
       </c>
     </row>
@@ -1760,11 +1772,11 @@
       <c r="C56" s="3">
         <v>171895</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7">
+      <c r="E56" s="10"/>
+      <c r="F56" s="11">
         <v>4.99</v>
       </c>
     </row>
@@ -1778,11 +1790,11 @@
       <c r="C57" s="3">
         <v>288034</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="7">
+      <c r="E57" s="10"/>
+      <c r="F57" s="11">
         <v>7.49</v>
       </c>
     </row>
@@ -1796,11 +1808,11 @@
       <c r="C58" s="3">
         <v>184034</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7">
+      <c r="E58" s="10"/>
+      <c r="F58" s="11">
         <v>5.49</v>
       </c>
     </row>
@@ -1814,11 +1826,11 @@
       <c r="C59" s="3">
         <v>239446</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="7">
+      <c r="E59" s="10"/>
+      <c r="F59" s="11">
         <f>12*3.06</f>
         <v>36.72</v>
       </c>
@@ -1833,11 +1845,11 @@
       <c r="C60" s="3">
         <v>168712</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="7">
+      <c r="E60" s="10"/>
+      <c r="F60" s="11">
         <f>15*3.2</f>
         <v>48</v>
       </c>
@@ -1852,11 +1864,11 @@
       <c r="C61" s="3">
         <v>313599</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="7">
+      <c r="E61" s="10"/>
+      <c r="F61" s="11">
         <f>15*3.69</f>
         <v>55.35</v>
       </c>
@@ -1871,11 +1883,11 @@
       <c r="C62" s="3">
         <v>102085</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="7">
+      <c r="E62" s="10"/>
+      <c r="F62" s="11">
         <v>12.99</v>
       </c>
     </row>
@@ -1889,11 +1901,11 @@
       <c r="C63" s="3">
         <v>301843</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="7">
+      <c r="E63" s="10"/>
+      <c r="F63" s="11">
         <v>78.989999999999995</v>
       </c>
     </row>
@@ -1907,11 +1919,11 @@
       <c r="C64" s="3">
         <v>102186</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="7">
+      <c r="E64" s="10"/>
+      <c r="F64" s="11">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -1925,11 +1937,11 @@
       <c r="C65" s="3">
         <v>107799</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="7">
+      <c r="E65" s="10"/>
+      <c r="F65" s="11">
         <v>10.99</v>
       </c>
     </row>
@@ -1943,11 +1955,11 @@
       <c r="C66" s="3">
         <v>102244</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="7">
+      <c r="E66" s="10"/>
+      <c r="F66" s="11">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -1961,11 +1973,11 @@
       <c r="C67" s="3">
         <v>102087</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E67" s="5"/>
-      <c r="F67" s="7">
+      <c r="E67" s="10"/>
+      <c r="F67" s="11">
         <v>49.99</v>
       </c>
     </row>
@@ -1979,11 +1991,11 @@
       <c r="C68" s="3">
         <v>137381</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="7">
+      <c r="E68" s="10"/>
+      <c r="F68" s="11">
         <v>132.99</v>
       </c>
     </row>
@@ -1997,11 +2009,11 @@
       <c r="C69" s="3">
         <v>102077</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="7">
+      <c r="E69" s="10"/>
+      <c r="F69" s="11">
         <v>189</v>
       </c>
     </row>
@@ -2015,11 +2027,11 @@
       <c r="C70" s="3">
         <v>102082</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="7">
+      <c r="E70" s="10"/>
+      <c r="F70" s="11">
         <v>75.989999999999995</v>
       </c>
     </row>
@@ -2033,11 +2045,11 @@
       <c r="C71" s="3">
         <v>109729</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="7">
+      <c r="E71" s="10"/>
+      <c r="F71" s="11">
         <v>99.99</v>
       </c>
     </row>
